--- a/server/data/combos.xlsx
+++ b/server/data/combos.xlsx
@@ -1,41 +1,209 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mayur\Desktop\WhoAmI\WhoAmI_Website\server\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B40436DB-92AA-40E2-AD42-03532D1018CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Combos" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="59">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>OriginalPrice</t>
+  </si>
+  <si>
+    <t>Material</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Tag</t>
+  </si>
+  <si>
+    <t>ImageURL</t>
+  </si>
+  <si>
+    <t>Wizarding Starter Bundle</t>
+  </si>
+  <si>
+    <t>HP - Sorting Hat + 2 Bookmarks + 3 Hanging Keys. The perfect entry into the wizarding world.</t>
+  </si>
+  <si>
+    <t>Premium PLA</t>
+  </si>
+  <si>
+    <t>Combos</t>
+  </si>
+  <si>
+    <t>Bestseller</t>
+  </si>
+  <si>
+    <t>/products/hp-combo-1/image.webp</t>
+  </si>
+  <si>
+    <t>Quidditch Captain Set</t>
+  </si>
+  <si>
+    <t>HP - Nimbus 2000 + Snitch Book Holder + 3 Hanging Keys. Gear up for the match of a lifetime.</t>
+  </si>
+  <si>
+    <t>Trending</t>
+  </si>
+  <si>
+    <t>/products/hp-combo-2/image.webp</t>
+  </si>
+  <si>
+    <t>The Chosen One Mega-Bundle</t>
+  </si>
+  <si>
+    <t>HP - Small Nimbus 2000 + Sorting Hat + Snitch holder + HP Booknook + 2 Bookmarks.</t>
+  </si>
+  <si>
+    <t>Identity</t>
+  </si>
+  <si>
+    <t>/products/hp-combo-3/image.webp</t>
+  </si>
+  <si>
+    <t>Keys to the Castle Set</t>
+  </si>
+  <si>
+    <t>HP - Complete Set of 9 Hanging Keys. Unlock the secrets of the wizarding world.</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>/products/hp-combo-4/image.webp</t>
+  </si>
+  <si>
+    <t>Hogwarts Reader Pack</t>
+  </si>
+  <si>
+    <t>HP - Snitch Book Holder + 2 Bookmarks + Maut ke Tohfe Keychain. For the dedicated bookworm.</t>
+  </si>
+  <si>
+    <t>/products/hp-combo-5/image.webp</t>
+  </si>
+  <si>
+    <t>Upside Down Trio</t>
+  </si>
+  <si>
+    <t>ST - Demadog + Demagorgon + Custom Wall Art. Bring Hawkins to your desk.</t>
+  </si>
+  <si>
+    <t>/products/st-combo-1/image.webp</t>
+  </si>
+  <si>
+    <t>Hawkins Explorer Set</t>
+  </si>
+  <si>
+    <t>ST - Demadog + 2 Bookmarks + Wall Art. Everything an explorer needs.</t>
+  </si>
+  <si>
+    <t>/products/st-combo-2/image.webp</t>
+  </si>
+  <si>
+    <t>Stranger Booklover Pack</t>
+  </si>
+  <si>
+    <t>ST - 2 Bookmarks + Themed Wall Art. Pure identity for your bookshelf.</t>
+  </si>
+  <si>
+    <t>/products/st-combo-3/image.webp</t>
+  </si>
+  <si>
+    <t>Iron Throne Mega-Set</t>
+  </si>
+  <si>
+    <t>GOT - Iron Throne + Dragon Eggs + House Bookmark. Rule over your workspace.</t>
+  </si>
+  <si>
+    <t>Premium PLA &amp; Resin</t>
+  </si>
+  <si>
+    <t>/products/got-combo-1/image.webp</t>
+  </si>
+  <si>
+    <t>Tatooine Bounty Pack</t>
+  </si>
+  <si>
+    <t>SW - Tatooine Diorama + Imperial Credit. For the galactic traveler.</t>
+  </si>
+  <si>
+    <t>/products/sw-combo-1/image.webp</t>
+  </si>
+  <si>
+    <t>Imperial Credit Stash</t>
+  </si>
+  <si>
+    <t>SW - Set of 4 Imperial Credits. Accumulate your wealth in some other galaxy.</t>
+  </si>
+  <si>
+    <t>/products/sw-combo-2/image.webp</t>
+  </si>
+  <si>
+    <t>Tactical Trainer Set (Full)</t>
+  </si>
+  <si>
+    <t>Butterfly Knife Series 1, 2, and 3. The complete collector set.</t>
+  </si>
+  <si>
+    <t>High-Impact PLA</t>
+  </si>
+  <si>
+    <t>/products/balisong-combo-1/image.webp</t>
+  </si>
+  <si>
+    <t>Knife Series 2 Set</t>
+  </si>
+  <si>
+    <t>Set of 3 Butterfly Knives from Series 2. Refined precision.</t>
+  </si>
+  <si>
+    <t>/products/balisong-combo-2/image.webp</t>
+  </si>
+  <si>
+    <t>Tactical Trio Series 3</t>
+  </si>
+  <si>
+    <t>Set of 3 Butterfly Knives from Series 3. The edge of craft.</t>
+  </si>
+  <si>
+    <t>/products/balisong-combo-3/image.webp</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -72,6 +240,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,47 +572,52 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="14.19921875" customWidth="1"/>
+    <col min="9" max="9" width="38.296875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Description</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Price</v>
-      </c>
-      <c r="E1" t="str">
-        <v>OriginalPrice</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Material</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Category</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Tag</v>
-      </c>
-      <c r="I1" t="str">
-        <v>ImageURL</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>101</v>
       </c>
-      <c r="B2" t="str">
-        <v>Wizarding Starter Bundle</v>
-      </c>
-      <c r="C2" t="str">
-        <v>HP - Sorting Hat + 2 Bookmarks + 3 Hanging Keys. The perfect entry into the wizarding world.</v>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
       </c>
       <c r="D2">
         <v>650</v>
@@ -444,28 +625,28 @@
       <c r="E2">
         <v>800</v>
       </c>
-      <c r="F2" t="str">
-        <v>Premium PLA</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Combos</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Bestseller</v>
-      </c>
-      <c r="I2" t="str">
-        <v>/products/hp-combo-1/image.webp</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>102</v>
       </c>
-      <c r="B3" t="str">
-        <v>Quidditch Captain Set</v>
-      </c>
-      <c r="C3" t="str">
-        <v>HP - Nimbus 2000 + Snitch Book Holder + 3 Hanging Keys. Gear up for the match of a lifetime.</v>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
       </c>
       <c r="D3">
         <v>700</v>
@@ -473,28 +654,28 @@
       <c r="E3">
         <v>950</v>
       </c>
-      <c r="F3" t="str">
-        <v>Premium PLA</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Combos</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Trending</v>
-      </c>
-      <c r="I3" t="str">
-        <v>/products/hp-combo-2/image.webp</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>103</v>
       </c>
-      <c r="B4" t="str">
-        <v>The Chosen One Mega-Bundle</v>
-      </c>
-      <c r="C4" t="str">
-        <v>HP - Small Nimbus 2000 + Sorting Hat + Snitch holder + HP Booknook + 2 Bookmarks.</v>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
       </c>
       <c r="D4">
         <v>2300</v>
@@ -502,28 +683,28 @@
       <c r="E4">
         <v>2750</v>
       </c>
-      <c r="F4" t="str">
-        <v>Premium PLA</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Combos</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Identity</v>
-      </c>
-      <c r="I4" t="str">
-        <v>/products/hp-combo-3/image.webp</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>104</v>
       </c>
-      <c r="B5" t="str">
-        <v>Keys to the Castle Set</v>
-      </c>
-      <c r="C5" t="str">
-        <v>HP - Complete Set of 9 Hanging Keys. Unlock the secrets of the wizarding world.</v>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
       </c>
       <c r="D5">
         <v>350</v>
@@ -531,28 +712,28 @@
       <c r="E5">
         <v>450</v>
       </c>
-      <c r="F5" t="str">
-        <v>Premium PLA</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Combos</v>
-      </c>
-      <c r="H5" t="str">
-        <v>New</v>
-      </c>
-      <c r="I5" t="str">
-        <v>/products/hp-combo-4/image.webp</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>105</v>
       </c>
-      <c r="B6" t="str">
-        <v>Hogwarts Reader Pack</v>
-      </c>
-      <c r="C6" t="str">
-        <v>HP - Snitch Book Holder + 2 Bookmarks + Maut ke Tohfe Keychain. For the dedicated bookworm.</v>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
       </c>
       <c r="D6">
         <v>500</v>
@@ -560,28 +741,28 @@
       <c r="E6">
         <v>650</v>
       </c>
-      <c r="F6" t="str">
-        <v>Premium PLA</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Combos</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Bestseller</v>
-      </c>
-      <c r="I6" t="str">
-        <v>/products/hp-combo-5/image.webp</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>106</v>
       </c>
-      <c r="B7" t="str">
-        <v>Upside Down Trio</v>
-      </c>
-      <c r="C7" t="str">
-        <v>ST - Demadog + Demagorgon + Custom Wall Art. Bring Hawkins to your desk.</v>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
       </c>
       <c r="D7">
         <v>1200</v>
@@ -589,28 +770,28 @@
       <c r="E7">
         <v>1400</v>
       </c>
-      <c r="F7" t="str">
-        <v>Premium PLA</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Combos</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Trending</v>
-      </c>
-      <c r="I7" t="str">
-        <v>/products/st-combo-1/image.webp</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>107</v>
       </c>
-      <c r="B8" t="str">
-        <v>Hawkins Explorer Set</v>
-      </c>
-      <c r="C8" t="str">
-        <v>ST - Demadog + 2 Bookmarks + Wall Art. Everything an explorer needs.</v>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
       </c>
       <c r="D8">
         <v>900</v>
@@ -618,28 +799,28 @@
       <c r="E8">
         <v>1030</v>
       </c>
-      <c r="F8" t="str">
-        <v>Premium PLA</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Combos</v>
-      </c>
-      <c r="H8" t="str">
-        <v>New</v>
-      </c>
-      <c r="I8" t="str">
-        <v>/products/st-combo-2/image.webp</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>108</v>
       </c>
-      <c r="B9" t="str">
-        <v>Stranger Booklover Pack</v>
-      </c>
-      <c r="C9" t="str">
-        <v>ST - 2 Bookmarks + Themed Wall Art. Pure identity for your bookshelf.</v>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
       </c>
       <c r="D9">
         <v>450</v>
@@ -647,28 +828,28 @@
       <c r="E9">
         <v>580</v>
       </c>
-      <c r="F9" t="str">
-        <v>Premium PLA</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Combos</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Bestseller</v>
-      </c>
-      <c r="I9" t="str">
-        <v>/products/st-combo-3/image.webp</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>109</v>
       </c>
-      <c r="B10" t="str">
-        <v>Iron Throne Mega-Set</v>
-      </c>
-      <c r="C10" t="str">
-        <v>GOT - Iron Throne + Dragon Eggs + House Bookmark. Rule over your workspace.</v>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
       </c>
       <c r="D10">
         <v>1300</v>
@@ -676,28 +857,28 @@
       <c r="E10">
         <v>1500</v>
       </c>
-      <c r="F10" t="str">
-        <v>Premium PLA &amp; Resin</v>
-      </c>
-      <c r="G10" t="str">
-        <v>Combos</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Identity</v>
-      </c>
-      <c r="I10" t="str">
-        <v>/products/got-combo-1/image.webp</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="F10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>110</v>
       </c>
-      <c r="B11" t="str">
-        <v>Tatooine Bounty Pack</v>
-      </c>
-      <c r="C11" t="str">
-        <v>SW - Tatooine Diorama + Imperial Credit. For the galactic traveler.</v>
+      <c r="B11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
       </c>
       <c r="D11">
         <v>1000</v>
@@ -705,28 +886,28 @@
       <c r="E11">
         <v>1100</v>
       </c>
-      <c r="F11" t="str">
-        <v>Premium PLA</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Combos</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Trending</v>
-      </c>
-      <c r="I11" t="str">
-        <v>/products/sw-combo-1/image.webp</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>111</v>
       </c>
-      <c r="B12" t="str">
-        <v>Imperial Credit Stash</v>
-      </c>
-      <c r="C12" t="str">
-        <v>SW - Set of 4 Imperial Credits. Accumulate your wealth in some other galaxy.</v>
+      <c r="B12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" t="s">
+        <v>47</v>
       </c>
       <c r="D12">
         <v>1000</v>
@@ -734,28 +915,28 @@
       <c r="E12">
         <v>1200</v>
       </c>
-      <c r="F12" t="str">
-        <v>Premium PLA</v>
-      </c>
-      <c r="G12" t="str">
-        <v>Combos</v>
-      </c>
-      <c r="H12" t="str">
-        <v>New</v>
-      </c>
-      <c r="I12" t="str">
-        <v>/products/sw-combo-2/image.webp</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>112</v>
       </c>
-      <c r="B13" t="str">
-        <v>Tactical Trainer Set (Full)</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Butterfly Knife Series 1, 2, and 3. The complete collector set.</v>
+      <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
       </c>
       <c r="D13">
         <v>800</v>
@@ -763,28 +944,28 @@
       <c r="E13">
         <v>1050</v>
       </c>
-      <c r="F13" t="str">
-        <v>High-Impact PLA</v>
-      </c>
-      <c r="G13" t="str">
-        <v>Combos</v>
-      </c>
-      <c r="H13" t="str">
-        <v>Bestseller</v>
-      </c>
-      <c r="I13" t="str">
-        <v>/products/balisong-combo-1/image.webp</v>
-      </c>
-    </row>
-    <row r="14">
+      <c r="F13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>113</v>
       </c>
-      <c r="B14" t="str">
-        <v>Knife Series 2 Set</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Set of 3 Butterfly Knives from Series 2. Refined precision.</v>
+      <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
+        <v>54</v>
       </c>
       <c r="D14">
         <v>600</v>
@@ -792,28 +973,28 @@
       <c r="E14">
         <v>750</v>
       </c>
-      <c r="F14" t="str">
-        <v>High-Impact PLA</v>
-      </c>
-      <c r="G14" t="str">
-        <v>Combos</v>
-      </c>
-      <c r="H14" t="str">
-        <v>New</v>
-      </c>
-      <c r="I14" t="str">
-        <v>/products/balisong-combo-2/image.webp</v>
-      </c>
-    </row>
-    <row r="15">
+      <c r="F14" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>114</v>
       </c>
-      <c r="B15" t="str">
-        <v>Tactical Trio Series 3</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Set of 3 Butterfly Knives from Series 3. The edge of craft.</v>
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
       </c>
       <c r="D15">
         <v>900</v>
@@ -821,22 +1002,23 @@
       <c r="E15">
         <v>1200</v>
       </c>
-      <c r="F15" t="str">
-        <v>High-Impact PLA</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Combos</v>
-      </c>
-      <c r="H15" t="str">
-        <v>Trending</v>
-      </c>
-      <c r="I15" t="str">
-        <v>/products/balisong-combo-3/image.webp</v>
+      <c r="F15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G15" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I15"/>
+    <ignoredError sqref="A1:I15" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>